--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.153.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.153.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.153.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.153.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œmust be liberally interpreted."."</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: and subpoena defendants.â€˜The subpoena under the above Orders 5 and</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]146</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]146</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L13: isolated marker/symbol line :: 146</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: F</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]146</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,14 +668,10 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: to order the service of the subp Ã¦ na</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Masterâ€™s Order 6 of 1851, might, with still more reason, be ordered to be</t>
-        </is>
-      </c>
+          <t>L113: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: a</t>
+          <t>L71: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -717,20 +717,20 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: of the subpÃ¦na out of the jurisdiction,</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="O4" s="1" t="inlineStr"/>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L112: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -764,17 +764,13 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: the service of a subp Ã¦ ena abroad, in</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: D</t>
+          <t>L113: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -811,15 +807,15 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: defendants. The subp Ã¦ na under th</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
-      <c r="N6" s="1" t="inlineStr"/>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>L128: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
       <c r="O6" s="1" t="inlineStr"/>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
@@ -854,11 +850,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: p Ã¦ na obtained on filing a bill.</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -897,11 +889,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: and subp Ã¦ na</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -940,11 +928,7 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
@@ -969,12 +953,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -983,11 +967,7 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: ubp Ã¦ na under the above Orders 5 and</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
@@ -1017,7 +997,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1026,11 +1006,7 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: p Ã¦ nas to ap</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
@@ -1055,12 +1031,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
